--- a/product_upload/packages/55/file.xlsx
+++ b/product_upload/packages/55/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -829,6 +834,11 @@
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>Finjuve</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>SKU-1B4D8817C824</t>
         </is>
@@ -849,7 +859,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1023,6 +1033,11 @@
         </is>
       </c>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>Xonvea</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>SKU-702D945B57E5</t>
         </is>
@@ -1043,7 +1058,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1197,6 +1212,11 @@
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
+        <is>
+          <t>Aztolyp</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>SKU-BD96D605272B</t>
         </is>
@@ -1217,7 +1237,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1379,6 +1399,11 @@
         </is>
       </c>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>Aztolyp</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>SKU-E5EF3B76C660</t>
         </is>
@@ -1399,7 +1424,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1557,6 +1582,11 @@
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t>Aztolyp</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>SKU-72536BF78409</t>
         </is>
@@ -1577,7 +1607,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1737,6 +1767,11 @@
         </is>
       </c>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>Figoya</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>SKU-4AC217084E85</t>
         </is>
@@ -1757,7 +1792,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1917,6 +1952,11 @@
         </is>
       </c>
       <c r="AT8" t="inlineStr">
+        <is>
+          <t>Inment</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>SKU-2A12AB08548A</t>
         </is>
@@ -1937,7 +1977,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2095,6 +2135,11 @@
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
+        <is>
+          <t>Lintra</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>SKU-D08FE00F8890</t>
         </is>
@@ -2115,7 +2160,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2271,6 +2316,11 @@
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
+        <is>
+          <t>Grateziano</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
         <is>
           <t>SKU-2AD304DD92F4</t>
         </is>
@@ -2291,7 +2341,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2445,6 +2495,11 @@
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
+        <is>
+          <t>Balanced Salt Solution 500ml</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>SKU-6A163654F909</t>
         </is>
@@ -2465,7 +2520,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2619,6 +2674,11 @@
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
+        <is>
+          <t>Acloran Plus</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>SKU-215AD554B599</t>
         </is>
@@ -2639,7 +2699,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2797,6 +2857,11 @@
         </is>
       </c>
       <c r="AT13" t="inlineStr">
+        <is>
+          <t>Acloran Plus</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>SKU-8AA014A626E3</t>
         </is>
@@ -2817,7 +2882,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2977,6 +3042,11 @@
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
+        <is>
+          <t>Stronyx</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>SKU-FEEF0F3ADE36</t>
         </is>
@@ -2997,7 +3067,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3161,6 +3231,11 @@
         </is>
       </c>
       <c r="AT15" t="inlineStr">
+        <is>
+          <t>Stronyx</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>SKU-FF2C3B6FF929</t>
         </is>
@@ -3181,7 +3256,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3339,6 +3414,11 @@
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
+        <is>
+          <t>Androgel</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
         <is>
           <t>SKU-63EF308A653C</t>
         </is>
@@ -3359,7 +3439,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3521,6 +3601,11 @@
         </is>
       </c>
       <c r="AT17" t="inlineStr">
+        <is>
+          <t>Tavneos</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>SKU-47CA1EEEE474</t>
         </is>
@@ -3541,7 +3626,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3701,6 +3786,11 @@
         </is>
       </c>
       <c r="AT18" t="inlineStr">
+        <is>
+          <t>Evrenzo</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
         <is>
           <t>SKU-6FF1E0975805</t>
         </is>
@@ -3721,7 +3811,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3883,6 +3973,11 @@
         </is>
       </c>
       <c r="AT19" t="inlineStr">
+        <is>
+          <t>Xeerun</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>SKU-6A00353FF320</t>
         </is>
@@ -3903,7 +3998,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4059,6 +4154,11 @@
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
+        <is>
+          <t>Tadalo</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>SKU-EFB9EE75F3CD</t>
         </is>
@@ -4079,7 +4179,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4249,6 +4349,11 @@
         </is>
       </c>
       <c r="AT21" t="inlineStr">
+        <is>
+          <t>DROLINA</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>SKU-CC8E2F976208</t>
         </is>
@@ -4269,7 +4374,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4435,6 +4540,11 @@
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
+        <is>
+          <t>DROLINA</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>SKU-20B9BB2A572B</t>
         </is>
@@ -4455,7 +4565,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4625,6 +4735,11 @@
         </is>
       </c>
       <c r="AT23" t="inlineStr">
+        <is>
+          <t>Vasrasti</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>SKU-21E4F04FA737</t>
         </is>
@@ -4645,7 +4760,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4811,6 +4926,11 @@
         </is>
       </c>
       <c r="AT24" t="inlineStr">
+        <is>
+          <t>Rocaltrol</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
         <is>
           <t>SKU-C7F61C219694</t>
         </is>
@@ -4831,7 +4951,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4987,6 +5107,11 @@
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
+        <is>
+          <t>Ticagard</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
         <is>
           <t>SKU-328261D5F8BF</t>
         </is>
@@ -5007,7 +5132,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5175,6 +5300,11 @@
         </is>
       </c>
       <c r="AT26" t="inlineStr">
+        <is>
+          <t>Flohale</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>SKU-768F15A66D7F</t>
         </is>
@@ -5195,7 +5325,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5363,6 +5493,11 @@
         </is>
       </c>
       <c r="AT27" t="inlineStr">
+        <is>
+          <t>Flohale</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>SKU-98856B3D8CB6</t>
         </is>
@@ -5383,7 +5518,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5543,6 +5678,11 @@
         </is>
       </c>
       <c r="AT28" t="inlineStr">
+        <is>
+          <t>Deeprub</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>SKU-A5EA1645B781</t>
         </is>
@@ -5563,7 +5703,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5723,6 +5863,11 @@
         </is>
       </c>
       <c r="AT29" t="inlineStr">
+        <is>
+          <t>Ambrolyt</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>SKU-7B9CDA11EBFD</t>
         </is>
@@ -5743,7 +5888,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5905,6 +6050,11 @@
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
+        <is>
+          <t>Rivaroxaban MCP</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>SKU-D9AEEB6C038D</t>
         </is>
@@ -5925,7 +6075,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6095,6 +6245,11 @@
         </is>
       </c>
       <c r="AT31" t="inlineStr">
+        <is>
+          <t>LIPRO SPRAY 10%</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>SKU-9BFC4CF4525C</t>
         </is>
@@ -6115,7 +6270,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6277,6 +6432,11 @@
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
+        <is>
+          <t>LIVTENCITY</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
         <is>
           <t>SKU-059F3FA85944</t>
         </is>
@@ -6297,7 +6457,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6459,6 +6619,11 @@
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
+        <is>
+          <t>Voriconazole MCP</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
         <is>
           <t>SKU-DB482C45340B</t>
         </is>
@@ -6479,7 +6644,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6645,6 +6810,11 @@
         </is>
       </c>
       <c r="AT34" t="inlineStr">
+        <is>
+          <t>Aquipta</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
         <is>
           <t>SKU-BCE2A2F1D195</t>
         </is>
@@ -6665,7 +6835,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6827,6 +6997,11 @@
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
+        <is>
+          <t>Aquipta</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>SKU-369672C2F4E8</t>
         </is>
@@ -6847,7 +7022,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7021,6 +7196,11 @@
         </is>
       </c>
       <c r="AT36" t="inlineStr">
+        <is>
+          <t>Suprax</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
         <is>
           <t>SKU-3049A74DD3F1</t>
         </is>
@@ -7041,7 +7221,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7201,6 +7381,11 @@
         </is>
       </c>
       <c r="AT37" t="inlineStr">
+        <is>
+          <t>Olmetrol Plus</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
         <is>
           <t>SKU-F0414BFC1BA6</t>
         </is>
@@ -7221,7 +7406,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7373,6 +7558,11 @@
       <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
+        <is>
+          <t>Olmetrol Plus</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
         <is>
           <t>SKU-3D5CA4C5A0B5</t>
         </is>
@@ -7393,7 +7583,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7549,6 +7739,11 @@
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olmetrol Plus </t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
         <is>
           <t>SKU-AF7E6FFF4FDD</t>
         </is>
@@ -7569,7 +7764,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7731,6 +7926,11 @@
         </is>
       </c>
       <c r="AT40" t="inlineStr">
+        <is>
+          <t>Cenoril</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
         <is>
           <t>SKU-3A4508A77546</t>
         </is>
@@ -7751,7 +7951,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7909,6 +8109,11 @@
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
+        <is>
+          <t>Diacerein</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
         <is>
           <t>SKU-D26E2307F701</t>
         </is>
@@ -7929,7 +8134,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8085,6 +8290,11 @@
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>SKU-7876B608D1EB</t>
         </is>
@@ -8105,7 +8315,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8267,6 +8477,11 @@
         </is>
       </c>
       <c r="AT43" t="inlineStr">
+        <is>
+          <t>Lavinda</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>SKU-DA0F792FE340</t>
         </is>
@@ -8287,7 +8502,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8445,6 +8660,11 @@
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
+        <is>
+          <t>Decozal</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
         <is>
           <t>SKU-C63B05801510</t>
         </is>
@@ -8465,7 +8685,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8623,6 +8843,11 @@
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
+        <is>
+          <t>Loanta</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>SKU-C0C46BEA841C</t>
         </is>
@@ -8643,7 +8868,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8809,6 +9034,11 @@
       <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
+        <is>
+          <t>Liptyn</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
         <is>
           <t>SKU-34469465DEB7</t>
         </is>
@@ -8829,7 +9059,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8989,6 +9219,11 @@
         </is>
       </c>
       <c r="AT47" t="inlineStr">
+        <is>
+          <t>ROSA</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>SKU-866EB2361ED0</t>
         </is>
@@ -9009,7 +9244,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9177,6 +9412,11 @@
         </is>
       </c>
       <c r="AT48" t="inlineStr">
+        <is>
+          <t>Meva SR</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
         <is>
           <t>SKU-70997337FC8A</t>
         </is>
@@ -9197,7 +9437,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9355,6 +9595,11 @@
       <c r="AR49" t="inlineStr"/>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
+        <is>
+          <t>Endura</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>SKU-E21EB7FEFD42</t>
         </is>
@@ -9375,7 +9620,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9541,6 +9786,11 @@
         </is>
       </c>
       <c r="AT50" t="inlineStr">
+        <is>
+          <t>Endura</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>SKU-CC2A3AA95DDC</t>
         </is>
@@ -9561,7 +9811,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9721,6 +9971,11 @@
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
+        <is>
+          <t>Cenoril</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>SKU-88B806374E02</t>
         </is>
@@ -9741,7 +9996,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9897,6 +10152,11 @@
       <c r="AR52" t="inlineStr"/>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
+        <is>
+          <t>Solfarin</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>SKU-7B27E1523CE9</t>
         </is>
@@ -9917,7 +10177,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10083,6 +10343,11 @@
         </is>
       </c>
       <c r="AT53" t="inlineStr">
+        <is>
+          <t>Apdx</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
         <is>
           <t>SKU-70448D0F305D</t>
         </is>
@@ -10103,7 +10368,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10269,6 +10534,11 @@
         </is>
       </c>
       <c r="AT54" t="inlineStr">
+        <is>
+          <t>Apdx</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
         <is>
           <t>SKU-C0F237400724</t>
         </is>
@@ -10289,7 +10559,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10449,6 +10719,11 @@
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
+        <is>
+          <t>Glandacet</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>SKU-6246C70493FD</t>
         </is>
@@ -10469,7 +10744,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10623,6 +10898,11 @@
       <c r="AR56" t="inlineStr"/>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
+        <is>
+          <t>Glandacet</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
         <is>
           <t>SKU-F004FEEA9C44</t>
         </is>
@@ -10643,7 +10923,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10805,6 +11085,11 @@
         </is>
       </c>
       <c r="AT57" t="inlineStr">
+        <is>
+          <t>Glandacet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
         <is>
           <t>SKU-301AB6CD69EE</t>
         </is>
@@ -10825,7 +11110,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11003,6 +11288,11 @@
         </is>
       </c>
       <c r="AT58" t="inlineStr">
+        <is>
+          <t>semglee</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
         <is>
           <t>SKU-3B97E06400BB</t>
         </is>
@@ -11023,7 +11313,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11185,6 +11475,11 @@
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
+        <is>
+          <t>Myteb</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
         <is>
           <t>SKU-77656C14846E</t>
         </is>
@@ -11205,7 +11500,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11363,6 +11658,11 @@
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
+        <is>
+          <t>Amgevita 20 mg per 0.4 ml</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>SKU-4238AB86EAFE</t>
         </is>
@@ -11383,7 +11683,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11549,6 +11849,11 @@
         </is>
       </c>
       <c r="AT61" t="inlineStr">
+        <is>
+          <t>Tyenne 162 mg per 0.9 ml</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
         <is>
           <t>SKU-EB0B5A950354</t>
         </is>
@@ -11569,7 +11874,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11727,6 +12032,11 @@
       <c r="AR62" t="inlineStr"/>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
+        <is>
+          <t>Tyenne 200 mg per 10 ml</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
         <is>
           <t>SKU-FB2168D0D32D</t>
         </is>
@@ -11747,7 +12057,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11909,6 +12219,11 @@
         </is>
       </c>
       <c r="AT63" t="inlineStr">
+        <is>
+          <t>iPAT</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
         <is>
           <t>SKU-24C2F2CCE82F</t>
         </is>
@@ -11929,7 +12244,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12087,6 +12402,11 @@
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
+        <is>
+          <t>Decozal menthol</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
         <is>
           <t>SKU-5B4B137E9765</t>
         </is>
@@ -12107,7 +12427,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12271,6 +12591,11 @@
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
+        <is>
+          <t>Adzoy</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
         <is>
           <t>SKU-515A252E2B6E</t>
         </is>
@@ -12291,7 +12616,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12453,6 +12778,11 @@
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
+        <is>
+          <t>Avysk</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
         <is>
           <t>SKU-F2CAA50E7947</t>
         </is>
@@ -12473,7 +12803,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12639,6 +12969,11 @@
         </is>
       </c>
       <c r="AT67" t="inlineStr">
+        <is>
+          <t>Avysk</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>SKU-B9B18F3BC132</t>
         </is>
@@ -12659,7 +12994,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12823,6 +13158,11 @@
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
+        <is>
+          <t>Nepexto</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>SKU-59747810C5F0</t>
         </is>
@@ -12843,7 +13183,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13011,6 +13351,11 @@
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
+        <is>
+          <t>Acumen</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>SKU-E4A8EF47DDD1</t>
         </is>
@@ -13031,7 +13376,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13199,6 +13544,11 @@
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
+        <is>
+          <t>Acumen</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>SKU-0FE1C1816183</t>
         </is>
@@ -13219,7 +13569,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13387,6 +13737,11 @@
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
+        <is>
+          <t>Acumen</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
         <is>
           <t>SKU-C1393222953D</t>
         </is>
@@ -13407,7 +13762,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13575,6 +13930,11 @@
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
+        <is>
+          <t>Acumen</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>SKU-FDC59E2E3683</t>
         </is>
@@ -13595,7 +13955,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13763,6 +14123,11 @@
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
+        <is>
+          <t>Acumen</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
         <is>
           <t>SKU-356DF3C07A7A</t>
         </is>
@@ -13783,7 +14148,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13957,6 +14322,11 @@
         </is>
       </c>
       <c r="AT74" t="inlineStr">
+        <is>
+          <t>DUCRESSA</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
         <is>
           <t>SKU-AA95EE507ECD</t>
         </is>
@@ -13977,7 +14347,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14139,6 +14509,11 @@
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
+        <is>
+          <t>Ecinq</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>SKU-EC8D92DF7C21</t>
         </is>
@@ -14159,7 +14534,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14321,6 +14696,11 @@
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
+        <is>
+          <t>Eulax</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
         <is>
           <t>SKU-E7E16B9116F0</t>
         </is>
@@ -14341,7 +14721,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14501,6 +14881,11 @@
         </is>
       </c>
       <c r="AT77" t="inlineStr">
+        <is>
+          <t>Rina Extra</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
         <is>
           <t>SKU-5F719820CE66</t>
         </is>
@@ -14521,7 +14906,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14677,6 +15062,11 @@
         </is>
       </c>
       <c r="AT78" t="inlineStr">
+        <is>
+          <t>Roxban</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
         <is>
           <t>SKU-C25B021AE484</t>
         </is>
@@ -14697,7 +15087,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14853,6 +15243,11 @@
         </is>
       </c>
       <c r="AT79" t="inlineStr">
+        <is>
+          <t>Roxban</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
         <is>
           <t>SKU-5ACCE62F4B8F</t>
         </is>
@@ -14873,7 +15268,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15021,6 +15416,11 @@
       <c r="AR80" t="inlineStr"/>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
+        <is>
+          <t>Roxban</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
         <is>
           <t>SKU-188CAB1A2861</t>
         </is>
@@ -15041,7 +15441,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15201,6 +15601,11 @@
         </is>
       </c>
       <c r="AT81" t="inlineStr">
+        <is>
+          <t>Abiraterone SPC</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
         <is>
           <t>SKU-F85F99FE8DDB</t>
         </is>
@@ -15221,7 +15626,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15379,6 +15784,11 @@
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
+        <is>
+          <t>Vizarsin</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
         <is>
           <t>SKU-2853CEC9E04B</t>
         </is>
@@ -15399,7 +15809,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15559,6 +15969,11 @@
         </is>
       </c>
       <c r="AT83" t="inlineStr">
+        <is>
+          <t>Linajent</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
         <is>
           <t>SKU-2C3F6A96A0C9</t>
         </is>
@@ -15579,7 +15994,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15749,6 +16164,11 @@
         </is>
       </c>
       <c r="AT84" t="inlineStr">
+        <is>
+          <t>Famotidine Amarox</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>SKU-B43543648BC4</t>
         </is>
@@ -15769,7 +16189,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15939,6 +16359,11 @@
         </is>
       </c>
       <c r="AT85" t="inlineStr">
+        <is>
+          <t>Famotidine Amarox</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>SKU-1BA32A973E77</t>
         </is>
@@ -15959,7 +16384,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16129,6 +16554,11 @@
         </is>
       </c>
       <c r="AT86" t="inlineStr">
+        <is>
+          <t>Famotidine Amarox</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
         <is>
           <t>SKU-6978C079461E</t>
         </is>
@@ -16149,7 +16579,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16311,6 +16741,11 @@
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
+        <is>
+          <t>Opsutin</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
         <is>
           <t>SKU-478F63C5B980</t>
         </is>
@@ -16331,7 +16766,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16507,6 +16942,11 @@
         </is>
       </c>
       <c r="AT88" t="inlineStr">
+        <is>
+          <t>Nepexto</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
         <is>
           <t>SKU-2E0137E67067</t>
         </is>
@@ -16527,7 +16967,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16691,6 +17131,11 @@
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
+        <is>
+          <t>Nepexto</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
         <is>
           <t>SKU-863224909A62</t>
         </is>
@@ -16711,7 +17156,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16867,6 +17312,11 @@
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
+        <is>
+          <t>Diaglipt</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
         <is>
           <t>SKU-7DD7FBDDD1A7</t>
         </is>
@@ -16887,7 +17337,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17051,6 +17501,11 @@
         </is>
       </c>
       <c r="AT91" t="inlineStr">
+        <is>
+          <t>abroten</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
         <is>
           <t>SKU-64A3E3AA6E6E</t>
         </is>
@@ -17071,7 +17526,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17235,6 +17690,11 @@
         </is>
       </c>
       <c r="AT92" t="inlineStr">
+        <is>
+          <t>abroten</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
         <is>
           <t>SKU-7B763FB1C220</t>
         </is>
@@ -17255,7 +17715,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17415,6 +17875,11 @@
       <c r="AR93" t="inlineStr"/>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
+        <is>
+          <t>Novanza</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
         <is>
           <t>SKU-AD543B3F401B</t>
         </is>
@@ -17435,7 +17900,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17593,6 +18058,11 @@
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
+        <is>
+          <t>Tqmint</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
         <is>
           <t>SKU-D15825EDC4E6</t>
         </is>
@@ -17613,7 +18083,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17767,6 +18237,11 @@
       <c r="AR95" t="inlineStr"/>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
+        <is>
+          <t>Tqmint</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
         <is>
           <t>SKU-FD9F87862256</t>
         </is>
@@ -17787,7 +18262,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17945,6 +18420,11 @@
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
+        <is>
+          <t>Tqmint</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
         <is>
           <t>SKU-00C22974FEFF</t>
         </is>
@@ -17965,7 +18445,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18121,6 +18601,11 @@
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
+        <is>
+          <t>Ralzyo</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
         <is>
           <t>SKU-653B2AB9235B</t>
         </is>
@@ -18141,7 +18626,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18301,6 +18786,11 @@
         </is>
       </c>
       <c r="AT98" t="inlineStr">
+        <is>
+          <t>Ralzyo</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
         <is>
           <t>SKU-A2FCF9F10D04</t>
         </is>
@@ -18321,7 +18811,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18473,6 +18963,11 @@
       <c r="AR99" t="inlineStr"/>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
+        <is>
+          <t>Cebatix</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>SKU-A2ACC5B58D57</t>
         </is>
@@ -18493,7 +18988,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18655,6 +19150,11 @@
         </is>
       </c>
       <c r="AT100" t="inlineStr">
+        <is>
+          <t>Bimatoprost BOS</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
         <is>
           <t>SKU-E15DDD5C79B7</t>
         </is>
@@ -18675,7 +19175,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18831,6 +19331,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Triova</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-3D7738D22E47</t>
         </is>
@@ -18847,7 +19352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18893,100 +19398,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19018,7 +19528,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19033,92 +19543,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-22999</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>423.78</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>541</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19150,7 +19665,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19165,92 +19680,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-99751</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>15.43</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>542</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19282,7 +19802,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19297,92 +19817,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-74711</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>460.02</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>543</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19414,7 +19939,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19429,92 +19954,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-40069</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>118.3</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>544</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19546,7 +20076,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19561,92 +20091,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-77633</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>204.59</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>545</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19678,7 +20213,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19693,92 +20228,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-30544</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>128.53</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>546</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19810,7 +20350,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19825,92 +20365,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-62388</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>321.83</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>547</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19942,7 +20487,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19957,92 +20502,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-18169</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>24.77</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>548</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20074,7 +20624,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20089,92 +20639,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-91177</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>177.96</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>549</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20206,7 +20761,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20221,92 +20776,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-95846</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>439.56</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>550</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20338,7 +20898,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20353,92 +20913,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-52000</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>268.27</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>551</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20455,7 +21020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20561,6 +21126,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20596,7 +21171,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20661,6 +21236,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-340368B6055F</t>
         </is>
@@ -20697,7 +21282,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20762,6 +21347,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-70E128860CC5</t>
         </is>
@@ -20798,7 +21393,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20863,6 +21458,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-3C318F599451</t>
         </is>
@@ -20899,7 +21504,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20964,6 +21569,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-77B47481EE72</t>
         </is>
@@ -21000,7 +21615,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21065,6 +21680,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-516AD50EEE8F</t>
         </is>
@@ -21101,7 +21726,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21166,6 +21791,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-7FBFF9FC175B</t>
         </is>
@@ -21202,7 +21837,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21267,6 +21902,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-5F841C726B93</t>
         </is>
@@ -21303,7 +21948,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21368,6 +22013,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-2205173F5887</t>
         </is>
@@ -21404,7 +22059,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21469,6 +22124,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-7BC63D7BC4E6</t>
         </is>
@@ -21505,7 +22170,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21570,6 +22235,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-6A448C2CB13F</t>
         </is>
@@ -21606,7 +22281,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21671,6 +22346,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-9202BB63C6B4</t>
         </is>
@@ -21707,7 +22392,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21772,6 +22457,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-9850E06B0461</t>
         </is>
@@ -21808,7 +22503,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21873,6 +22568,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CC17AD52EA08</t>
         </is>
@@ -21909,7 +22614,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21974,6 +22679,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-40D0FAC8334E</t>
         </is>
@@ -22010,7 +22725,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22075,6 +22790,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-15CDDF49C648</t>
         </is>
@@ -22111,7 +22836,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22176,6 +22901,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-B7B8D680663B</t>
         </is>
@@ -22212,7 +22947,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22277,6 +23012,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-AE06857D247A</t>
         </is>
@@ -22313,7 +23058,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22378,6 +23123,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-5E2A3D6ABA86</t>
         </is>
@@ -22414,7 +23169,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22479,6 +23234,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-7421BDA52959</t>
         </is>
@@ -22515,7 +23280,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22580,6 +23345,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-5CC7D2184D1B</t>
         </is>

--- a/product_upload/packages/55/file.xlsx
+++ b/product_upload/packages/55/file.xlsx
@@ -682,8 +682,16 @@
           <t>5404465824-567-341000180148</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Finjuve</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Finjuve detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -1066,8 +1074,16 @@
           <t>6420490576-346-258306964827</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aztolyp</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aztolyp detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1245,8 +1261,16 @@
           <t>3257352586-633-325328859320</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aztolyp</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aztolyp detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1432,8 +1456,16 @@
           <t>0302738088-817-661520292808</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aztolyp</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Aztolyp detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1615,8 +1647,16 @@
           <t>3864081257-631-174982215194</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Figoya</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Figoya detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1800,8 +1840,16 @@
           <t>4977856475-534-955143059763</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Inment</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Inment detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1985,8 +2033,16 @@
           <t>3154088108-106-975703734197</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lintra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lintra detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2168,8 +2224,16 @@
           <t>8317974261-113-586805874357</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Grateziano</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Grateziano detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2349,8 +2413,16 @@
           <t>0861962577-180-719129969715</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Balanced Salt Solution 500ml</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Balanced Salt Solution 500ml detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2528,8 +2600,16 @@
           <t>4026786585-399-055990550468</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Acloran Plus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Acloran Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2707,8 +2787,16 @@
           <t>0383072012-711-879083178019</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Acloran Plus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Acloran Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -2890,8 +2978,16 @@
           <t>2994888235-291-531728440436</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Stronyx</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Stronyx detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -3075,8 +3171,16 @@
           <t>1255091021-051-708093043050</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Stronyx</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Stronyx detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -3264,8 +3368,16 @@
           <t>1305418513-867-292755619517</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Androgel</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Androgel detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3447,8 +3559,16 @@
           <t>3545246204-551-338258247382</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tavneos</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Tavneos detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3634,8 +3754,16 @@
           <t>1199475415-158-924414385593</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Evrenzo</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Evrenzo detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3819,8 +3947,16 @@
           <t>0533261069-823-259850395409</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xeerun</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Xeerun detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4006,8 +4142,16 @@
           <t>1878969724-795-209146465127</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadalo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Tadalo detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4768,8 +4912,16 @@
           <t>3501720833-768-900482759738</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rocaltrol</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Rocaltrol detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -4959,8 +5111,16 @@
           <t>1970079212-674-814824873401</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ticagard</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ticagard detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -5526,8 +5686,16 @@
           <t>3776529247-054-432945837582</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Deeprub</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Deeprub detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5711,8 +5879,16 @@
           <t>7030786345-659-376682870663</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ambrolyt</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Ambrolyt detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5896,8 +6072,16 @@
           <t>9750722998-487-406280271336</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rivaroxaban MCP</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Rivaroxaban MCP detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6278,8 +6462,16 @@
           <t>0862450619-179-477647051263</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIVTENCITY</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>LIVTENCITY detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6465,8 +6657,16 @@
           <t>4659546310-164-245402339177</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Voriconazole MCP</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Voriconazole MCP detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6652,8 +6852,16 @@
           <t>9188367680-045-650633357510</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aquipta</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Aquipta detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6843,8 +7051,16 @@
           <t>5058331633-634-781501929307</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aquipta</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Aquipta detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7229,8 +7445,16 @@
           <t>2274060352-240-861683158555</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmetrol Plus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Olmetrol Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7414,8 +7638,16 @@
           <t>7936340005-553-383926491487</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmetrol Plus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Olmetrol Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7591,8 +7823,16 @@
           <t>2233707865-258-175112756502</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmetrol Plus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Olmetrol Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7772,8 +8012,16 @@
           <t>7689915557-688-535295383610</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cenoril</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Cenoril detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7959,8 +8207,16 @@
           <t>6939570966-618-972341943805</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Diacerein</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Diacerein detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8142,8 +8398,16 @@
           <t>5911885915-790-083708893622</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROSA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ROSA detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8323,8 +8587,16 @@
           <t>2864375291-063-020335074057</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lavinda</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Lavinda detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8510,8 +8782,16 @@
           <t>3429090249-336-068734766490</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Decozal</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Decozal detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8693,8 +8973,16 @@
           <t>0622553896-939-374182647503</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Loanta</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Loanta detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9067,8 +9355,16 @@
           <t>9222239746-860-409396388597</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROSA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ROSA detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9445,8 +9741,16 @@
           <t>1778971418-050-621497778472</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Endura</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Endura detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9628,8 +9932,16 @@
           <t>8334424488-818-182447986729</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Endura</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Endura detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10004,8 +10316,16 @@
           <t>8349737639-382-128087551373</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Solfarin</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Solfarin detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10185,8 +10505,16 @@
           <t>7266466752-882-147067697372</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apdx</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Apdx detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10376,8 +10704,16 @@
           <t>6815591233-620-433123340648</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apdx</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Apdx detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10567,8 +10903,16 @@
           <t>5564972088-837-527349671482</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glandacet</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Glandacet detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -10752,8 +11096,16 @@
           <t>8220078009-227-461153923089</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glandacet</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Glandacet detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -10931,8 +11283,16 @@
           <t>4915347791-991-725370494995</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glandacet</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Glandacet detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>Pharma Pharmaceutical Industries (PPI)</t>
@@ -11321,8 +11681,16 @@
           <t>5842219219-948-849121747603</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Myteb</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Myteb detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11508,8 +11876,16 @@
           <t>6818281139-966-516762882474</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amgevita 20 mg per 0.4 ml</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Amgevita 20 mg per 0.4 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11691,8 +12067,16 @@
           <t>7678017414-645-977735024581</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tyenne 162 mg per 0.9 ml</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tyenne 162 mg per 0.9 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -11882,8 +12266,16 @@
           <t>2463296880-603-257741226025</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tyenne 200 mg per 10 ml</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Tyenne 200 mg per 10 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -12065,8 +12457,16 @@
           <t>7041618475-869-797585777749</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ iPAT</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>iPAT detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12252,8 +12652,16 @@
           <t>5203670859-437-177008953394</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Decozal menthol</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Decozal menthol detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12624,8 +13032,16 @@
           <t>1311462153-131-018210064318</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avysk</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Avysk detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12811,8 +13227,16 @@
           <t>8549071414-173-760891292723</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avysk</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Avysk detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13002,8 +13426,16 @@
           <t>9488219142-951-774227894730</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nepexto</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Nepexto detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -14355,8 +14787,16 @@
           <t>0301180816-123-906793077674</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ecinq</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Ecinq detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14542,8 +14982,16 @@
           <t>9592472921-184-108845716100</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Eulax</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Eulax detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14729,8 +15177,16 @@
           <t>5947587182-927-943743695105</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rina Extra</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Rina Extra detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14914,8 +15370,16 @@
           <t>7549345252-406-954858097390</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Roxban</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Roxban detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15095,8 +15559,16 @@
           <t>0997039103-938-721346007919</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Roxban</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Roxban detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15276,8 +15748,16 @@
           <t>0022566228-024-243347523404</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Roxban</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Roxban detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15449,8 +15929,16 @@
           <t>5243180760-932-583649943942</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Abiraterone SPC</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Abiraterone SPC detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15634,8 +16122,16 @@
           <t>4435048403-861-920885422163</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vizarsin</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Vizarsin detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15817,8 +16313,16 @@
           <t>0025170847-771-748291898760</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Linajent</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Linajent detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16587,8 +17091,16 @@
           <t>1042966428-532-705637924092</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Opsutin</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Opsutin detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16975,8 +17487,16 @@
           <t>7749553187-823-831830267389</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nepexto</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Nepexto detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -17164,8 +17684,16 @@
           <t>6379884307-665-324475063460</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Diaglipt</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Diaglipt detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17908,8 +18436,16 @@
           <t>9256886812-560-328976530153</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tqmint</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Tqmint detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18091,8 +18627,16 @@
           <t>1646096664-623-119084390790</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tqmint</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Tqmint detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18270,8 +18814,16 @@
           <t>9751782742-326-481536704986</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tqmint</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Tqmint detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18453,8 +19005,16 @@
           <t>4854482521-234-664526796060</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ralzyo</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ralzyo detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18634,8 +19194,16 @@
           <t>3552980211-210-570043543686</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ralzyo</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ralzyo detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18819,8 +19387,16 @@
           <t>9383471663-745-252694017411</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cebatix</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Cebatix detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -18996,8 +19572,16 @@
           <t>9706932350-610-701956782924</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bimatoprost BOS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bimatoprost BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19183,8 +19767,16 @@
           <t>7818961274-121-776305596439</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Triova</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Triova detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/55/file.xlsx
+++ b/product_upload/packages/55/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21612,7 +21612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21693,40 +21693,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21806,38 +21811,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>154.66</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-340368B6055F</t>
         </is>
@@ -21917,38 +21927,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>279.11</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-70E128860CC5</t>
         </is>
@@ -22028,38 +22043,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>145.49</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-3C318F599451</t>
         </is>
@@ -22139,38 +22159,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>28.47</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-77B47481EE72</t>
         </is>
@@ -22250,38 +22275,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>208.66</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-516AD50EEE8F</t>
         </is>
@@ -22361,38 +22391,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>490.54</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-7FBFF9FC175B</t>
         </is>
@@ -22472,38 +22507,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>222.95</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-5F841C726B93</t>
         </is>
@@ -22583,38 +22623,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>486.57</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-2205173F5887</t>
         </is>
@@ -22694,38 +22739,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>400.66</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-7BC63D7BC4E6</t>
         </is>
@@ -22805,38 +22855,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>137.04</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-6A448C2CB13F</t>
         </is>
@@ -22916,38 +22971,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>138.64</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-9202BB63C6B4</t>
         </is>
@@ -23027,38 +23087,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>332.48</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-9850E06B0461</t>
         </is>
@@ -23138,38 +23203,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>283.96</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CC17AD52EA08</t>
         </is>
@@ -23249,38 +23319,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>426.93</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-40D0FAC8334E</t>
         </is>
@@ -23360,38 +23435,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>195.33</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-15CDDF49C648</t>
         </is>
@@ -23471,38 +23551,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>34.41</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-B7B8D680663B</t>
         </is>
@@ -23582,38 +23667,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>429.06</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-AE06857D247A</t>
         </is>
@@ -23693,38 +23783,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>87.84</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-5E2A3D6ABA86</t>
         </is>
@@ -23804,38 +23899,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>148.28</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-7421BDA52959</t>
         </is>
@@ -23915,38 +24015,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>90.36</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-5CC7D2184D1B</t>
         </is>
